--- a/pipeline/credit_rating/output/xhtn_tong_hop_20261030.xlsx
+++ b/pipeline/credit_rating/output/xhtn_tong_hop_20261030.xlsx
@@ -707,7 +707,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:55</t>
+          <t>2026-10-30 15:13:46</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:55</t>
+          <t>2026-10-30 15:13:46</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24:09</t>
+          <t>2026-10-30 15:14:02</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24:09</t>
+          <t>2026-10-30 15:14:02</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24:09</t>
+          <t>2026-10-30 15:14:02</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24:09</t>
+          <t>2026-10-30 15:14:02</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24:09</t>
+          <t>2026-10-30 15:14:02</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24:09</t>
+          <t>2026-10-30 15:14:02</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:57</t>
+          <t>2026-10-30 15:13:47</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -2539,7 +2539,7 @@
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -2627,7 +2627,7 @@
       <c r="AD19" t="inlineStr"/>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -3091,7 +3091,7 @@
       <c r="AD23" t="inlineStr"/>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
@@ -3553,7 +3553,7 @@
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
@@ -3675,7 +3675,7 @@
       <c r="AD28" t="inlineStr"/>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
@@ -3807,7 +3807,7 @@
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
@@ -4247,7 +4247,7 @@
       <c r="AD33" t="inlineStr"/>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
@@ -4335,7 +4335,7 @@
       <c r="AD34" t="inlineStr"/>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="AE37" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24:09</t>
+          <t>2026-10-30 15:14:02</t>
         </is>
       </c>
       <c r="AF37" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="AE38" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24:09</t>
+          <t>2026-10-30 15:14:02</t>
         </is>
       </c>
       <c r="AF38" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="AE39" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24:09</t>
+          <t>2026-10-30 15:14:02</t>
         </is>
       </c>
       <c r="AF39" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="AE40" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF40" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="AE41" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
@@ -5367,7 +5367,7 @@
       <c r="AD43" t="inlineStr"/>
       <c r="AE43" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="AE44" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="AE46" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF46" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="AE47" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF47" t="inlineStr">
@@ -5919,7 +5919,7 @@
       <c r="AD48" t="inlineStr"/>
       <c r="AE48" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF48" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="AE49" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF49" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="AE50" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF50" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="AE51" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF51" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="AE52" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF52" t="inlineStr">
@@ -6485,7 +6485,7 @@
       </c>
       <c r="AE53" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24:09</t>
+          <t>2026-10-30 15:14:02</t>
         </is>
       </c>
       <c r="AF53" t="inlineStr">
@@ -6595,7 +6595,7 @@
       </c>
       <c r="AE54" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:55</t>
+          <t>2026-10-30 15:13:46</t>
         </is>
       </c>
       <c r="AF54" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="AE55" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF55" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="AE56" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF56" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="AE57" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF57" t="inlineStr">
@@ -7019,7 +7019,7 @@
       <c r="AD58" t="inlineStr"/>
       <c r="AE58" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF58" t="inlineStr">
@@ -7141,7 +7141,7 @@
       <c r="AD59" t="inlineStr"/>
       <c r="AE59" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF59" t="inlineStr">
@@ -7253,7 +7253,7 @@
       </c>
       <c r="AE60" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:57</t>
+          <t>2026-10-30 15:13:47</t>
         </is>
       </c>
       <c r="AF60" t="inlineStr">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="AE61" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:57</t>
+          <t>2026-10-30 15:13:47</t>
         </is>
       </c>
       <c r="AF61" t="inlineStr">
@@ -7475,7 +7475,7 @@
       </c>
       <c r="AE62" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF62" t="inlineStr">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="AE63" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF63" t="inlineStr">
@@ -7703,7 +7703,7 @@
       </c>
       <c r="AE64" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF64" t="inlineStr">
@@ -7787,7 +7787,7 @@
       <c r="AD65" t="inlineStr"/>
       <c r="AE65" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF65" t="inlineStr">
@@ -7871,7 +7871,7 @@
       <c r="AD66" t="inlineStr"/>
       <c r="AE66" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF66" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AE67" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF67" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="AE68" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF68" t="inlineStr">
@@ -8215,7 +8215,7 @@
       </c>
       <c r="AE69" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF69" t="inlineStr">
@@ -8347,7 +8347,7 @@
       </c>
       <c r="AE70" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF70" t="inlineStr">
@@ -8475,7 +8475,7 @@
       </c>
       <c r="AE71" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF71" t="inlineStr">
@@ -8585,7 +8585,7 @@
       </c>
       <c r="AE72" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF72" t="inlineStr">
@@ -8695,7 +8695,7 @@
       </c>
       <c r="AE73" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF73" t="inlineStr">
@@ -8805,7 +8805,7 @@
       </c>
       <c r="AE74" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF74" t="inlineStr">
@@ -8933,7 +8933,7 @@
       </c>
       <c r="AE75" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF75" t="inlineStr">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="AE76" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF76" t="inlineStr">
@@ -9131,7 +9131,7 @@
       <c r="AD77" t="inlineStr"/>
       <c r="AE77" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF77" t="inlineStr">
@@ -9219,7 +9219,7 @@
       <c r="AD78" t="inlineStr"/>
       <c r="AE78" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF78" t="inlineStr">
@@ -9339,7 +9339,7 @@
       </c>
       <c r="AE79" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF79" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="AE80" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF80" t="inlineStr">
@@ -9563,7 +9563,7 @@
       </c>
       <c r="AE81" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF81" t="inlineStr">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="AE82" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24:09</t>
+          <t>2026-10-30 15:14:02</t>
         </is>
       </c>
       <c r="AF82" t="inlineStr">
@@ -9789,7 +9789,7 @@
       <c r="AD83" t="inlineStr"/>
       <c r="AE83" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24:09</t>
+          <t>2026-10-30 15:14:02</t>
         </is>
       </c>
       <c r="AF83" t="inlineStr">
@@ -9905,7 +9905,7 @@
       </c>
       <c r="AE84" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24:09</t>
+          <t>2026-10-30 15:14:02</t>
         </is>
       </c>
       <c r="AF84" t="inlineStr">
@@ -10015,7 +10015,7 @@
       <c r="AD85" t="inlineStr"/>
       <c r="AE85" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24:09</t>
+          <t>2026-10-30 15:14:02</t>
         </is>
       </c>
       <c r="AF85" t="inlineStr">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="AE86" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF86" t="inlineStr">
@@ -10257,7 +10257,7 @@
       </c>
       <c r="AE87" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF87" t="inlineStr">
@@ -10371,7 +10371,7 @@
       </c>
       <c r="AE88" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF88" t="inlineStr">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="AE89" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF89" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="AE90" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF90" t="inlineStr">
@@ -10719,7 +10719,7 @@
       </c>
       <c r="AE91" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF91" t="inlineStr">
@@ -10833,7 +10833,7 @@
       </c>
       <c r="AE92" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF92" t="inlineStr">
@@ -10949,7 +10949,7 @@
       </c>
       <c r="AE93" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24:09</t>
+          <t>2026-10-30 15:14:02</t>
         </is>
       </c>
       <c r="AF93" t="inlineStr">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="AE94" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF94" t="inlineStr">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="AE95" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF95" t="inlineStr">
@@ -11305,7 +11305,7 @@
       </c>
       <c r="AE96" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF96" t="inlineStr">
@@ -11417,7 +11417,7 @@
       </c>
       <c r="AE97" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF97" t="inlineStr">
@@ -11531,7 +11531,7 @@
       </c>
       <c r="AE98" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF98" t="inlineStr">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="AE99" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF99" t="inlineStr">
@@ -11765,7 +11765,7 @@
       </c>
       <c r="AE100" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF100" t="inlineStr">
@@ -11875,7 +11875,7 @@
       </c>
       <c r="AE101" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF101" t="inlineStr">
@@ -11991,7 +11991,7 @@
       </c>
       <c r="AE102" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24:09</t>
+          <t>2026-10-30 15:14:02</t>
         </is>
       </c>
       <c r="AF102" t="inlineStr">
@@ -12101,7 +12101,7 @@
       </c>
       <c r="AE103" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF103" t="inlineStr">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="AE104" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF104" t="inlineStr">
@@ -12335,7 +12335,7 @@
       </c>
       <c r="AE105" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF105" t="inlineStr">
@@ -12445,7 +12445,7 @@
       </c>
       <c r="AE106" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF106" t="inlineStr">
@@ -12555,7 +12555,7 @@
       </c>
       <c r="AE107" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF107" t="inlineStr">
@@ -12665,7 +12665,7 @@
       </c>
       <c r="AE108" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF108" t="inlineStr">
@@ -12765,7 +12765,7 @@
       </c>
       <c r="AE109" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF109" t="inlineStr">
@@ -12875,7 +12875,7 @@
       </c>
       <c r="AE110" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF110" t="inlineStr">
@@ -12987,7 +12987,7 @@
       </c>
       <c r="AE111" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF111" t="inlineStr">
@@ -13097,7 +13097,7 @@
       </c>
       <c r="AE112" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF112" t="inlineStr">
@@ -13207,7 +13207,7 @@
       </c>
       <c r="AE113" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF113" t="inlineStr">
@@ -13323,7 +13323,7 @@
       </c>
       <c r="AE114" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF114" t="inlineStr">
@@ -13455,7 +13455,7 @@
       </c>
       <c r="AE115" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF115" t="inlineStr">
@@ -13583,7 +13583,7 @@
       </c>
       <c r="AE116" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF116" t="inlineStr">
@@ -13715,7 +13715,7 @@
       </c>
       <c r="AE117" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF117" t="inlineStr">
@@ -13843,7 +13843,7 @@
       </c>
       <c r="AE118" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF118" t="inlineStr">
@@ -13953,7 +13953,7 @@
       </c>
       <c r="AE119" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF119" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="AE120" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF120" t="inlineStr">
@@ -14181,7 +14181,7 @@
       </c>
       <c r="AE121" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF121" t="inlineStr">
@@ -14295,7 +14295,7 @@
       </c>
       <c r="AE122" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF122" t="inlineStr">
@@ -14415,7 +14415,7 @@
       </c>
       <c r="AE123" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF123" t="inlineStr">
@@ -14515,7 +14515,7 @@
       </c>
       <c r="AE124" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF124" t="inlineStr">
@@ -14629,7 +14629,7 @@
       </c>
       <c r="AE125" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF125" t="inlineStr">
@@ -14745,7 +14745,7 @@
       </c>
       <c r="AE126" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24:09</t>
+          <t>2026-10-30 15:14:02</t>
         </is>
       </c>
       <c r="AF126" t="inlineStr">
@@ -14855,7 +14855,7 @@
       </c>
       <c r="AE127" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF127" t="inlineStr">
@@ -14969,7 +14969,7 @@
       </c>
       <c r="AE128" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF128" t="inlineStr">
@@ -15083,7 +15083,7 @@
       </c>
       <c r="AE129" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF129" t="inlineStr">
@@ -15211,7 +15211,7 @@
       </c>
       <c r="AE130" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF130" t="inlineStr">
@@ -15327,7 +15327,7 @@
       </c>
       <c r="AE131" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF131" t="inlineStr">
@@ -15423,7 +15423,7 @@
       </c>
       <c r="AE132" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF132" t="inlineStr">
@@ -15533,7 +15533,7 @@
       </c>
       <c r="AE133" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF133" t="inlineStr">
@@ -15633,7 +15633,7 @@
       </c>
       <c r="AE134" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF134" t="inlineStr">
@@ -15747,7 +15747,7 @@
       </c>
       <c r="AE135" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF135" t="inlineStr">
@@ -15861,7 +15861,7 @@
       </c>
       <c r="AE136" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF136" t="inlineStr">
@@ -15961,7 +15961,7 @@
       </c>
       <c r="AE137" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF137" t="inlineStr">
@@ -16071,7 +16071,7 @@
       </c>
       <c r="AE138" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:55</t>
+          <t>2026-10-30 15:13:46</t>
         </is>
       </c>
       <c r="AF138" t="inlineStr">
@@ -16181,7 +16181,7 @@
       </c>
       <c r="AE139" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF139" t="inlineStr">
@@ -16295,7 +16295,7 @@
       </c>
       <c r="AE140" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF140" t="inlineStr">
@@ -16409,7 +16409,7 @@
       </c>
       <c r="AE141" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF141" t="inlineStr">
@@ -16519,7 +16519,7 @@
       </c>
       <c r="AE142" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF142" t="inlineStr">
@@ -16633,7 +16633,7 @@
       </c>
       <c r="AE143" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF143" t="inlineStr">
@@ -16743,7 +16743,7 @@
       </c>
       <c r="AE144" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:55</t>
+          <t>2026-10-30 15:13:46</t>
         </is>
       </c>
       <c r="AF144" t="inlineStr">
@@ -16853,7 +16853,7 @@
       </c>
       <c r="AE145" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:55</t>
+          <t>2026-10-30 15:13:46</t>
         </is>
       </c>
       <c r="AF145" t="inlineStr">
@@ -16977,7 +16977,7 @@
       </c>
       <c r="AE146" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:57</t>
+          <t>2026-10-30 15:13:47</t>
         </is>
       </c>
       <c r="AF146" t="inlineStr">
@@ -17087,7 +17087,7 @@
       </c>
       <c r="AE147" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF147" t="inlineStr">
@@ -17201,7 +17201,7 @@
       </c>
       <c r="AE148" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF148" t="inlineStr">
@@ -17315,7 +17315,7 @@
       </c>
       <c r="AE149" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF149" t="inlineStr">
@@ -17429,7 +17429,7 @@
       </c>
       <c r="AE150" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF150" t="inlineStr">
@@ -17541,7 +17541,7 @@
       </c>
       <c r="AE151" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF151" t="inlineStr">
@@ -17657,7 +17657,7 @@
       </c>
       <c r="AE152" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24:09</t>
+          <t>2026-10-30 15:14:02</t>
         </is>
       </c>
       <c r="AF152" t="inlineStr">
@@ -17767,7 +17767,7 @@
       </c>
       <c r="AE153" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF153" t="inlineStr">
@@ -17877,7 +17877,7 @@
       </c>
       <c r="AE154" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF154" t="inlineStr">
@@ -17991,7 +17991,7 @@
       </c>
       <c r="AE155" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:55</t>
+          <t>2026-10-30 15:13:46</t>
         </is>
       </c>
       <c r="AF155" t="inlineStr">
@@ -18115,7 +18115,7 @@
       </c>
       <c r="AE156" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF156" t="inlineStr">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="AE157" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF157" t="inlineStr">
@@ -18355,7 +18355,7 @@
       </c>
       <c r="AE158" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF158" t="inlineStr">
@@ -18487,7 +18487,7 @@
       </c>
       <c r="AE159" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF159" t="inlineStr">
@@ -18611,7 +18611,7 @@
       </c>
       <c r="AE160" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF160" t="inlineStr">
@@ -18735,7 +18735,7 @@
       </c>
       <c r="AE161" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF161" t="inlineStr">
@@ -18835,7 +18835,7 @@
       </c>
       <c r="AE162" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF162" t="inlineStr">
@@ -18955,7 +18955,7 @@
       </c>
       <c r="AE163" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF163" t="inlineStr">
@@ -19083,7 +19083,7 @@
       </c>
       <c r="AE164" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF164" t="inlineStr">
@@ -19197,7 +19197,7 @@
       </c>
       <c r="AE165" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF165" t="inlineStr">
@@ -19311,7 +19311,7 @@
       </c>
       <c r="AE166" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF166" t="inlineStr">
@@ -19425,7 +19425,7 @@
       </c>
       <c r="AE167" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF167" t="inlineStr">
@@ -19535,7 +19535,7 @@
       </c>
       <c r="AE168" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF168" t="inlineStr">
@@ -19649,7 +19649,7 @@
       </c>
       <c r="AE169" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF169" t="inlineStr">
@@ -19763,7 +19763,7 @@
       </c>
       <c r="AE170" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF170" t="inlineStr">
@@ -19877,7 +19877,7 @@
       </c>
       <c r="AE171" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF171" t="inlineStr">
@@ -19991,7 +19991,7 @@
       </c>
       <c r="AE172" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF172" t="inlineStr">
@@ -20111,7 +20111,7 @@
       </c>
       <c r="AE173" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF173" t="inlineStr">
@@ -20227,7 +20227,7 @@
       </c>
       <c r="AE174" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24:09</t>
+          <t>2026-10-30 15:14:02</t>
         </is>
       </c>
       <c r="AF174" t="inlineStr">
@@ -20337,7 +20337,7 @@
       </c>
       <c r="AE175" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF175" t="inlineStr">
@@ -20457,7 +20457,7 @@
       </c>
       <c r="AE176" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF176" t="inlineStr">
@@ -20589,7 +20589,7 @@
       </c>
       <c r="AE177" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF177" t="inlineStr">
@@ -20717,7 +20717,7 @@
       </c>
       <c r="AE178" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF178" t="inlineStr">
@@ -20829,7 +20829,7 @@
       </c>
       <c r="AE179" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF179" t="inlineStr">
@@ -20939,7 +20939,7 @@
       </c>
       <c r="AE180" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF180" t="inlineStr">
@@ -21049,7 +21049,7 @@
       </c>
       <c r="AE181" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF181" t="inlineStr">
@@ -21159,7 +21159,7 @@
       </c>
       <c r="AE182" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF182" t="inlineStr">
@@ -21269,7 +21269,7 @@
       </c>
       <c r="AE183" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:55</t>
+          <t>2026-10-30 15:13:46</t>
         </is>
       </c>
       <c r="AF183" t="inlineStr">
@@ -21381,7 +21381,7 @@
       </c>
       <c r="AE184" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF184" t="inlineStr">
@@ -21497,7 +21497,7 @@
       </c>
       <c r="AE185" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF185" t="inlineStr">
@@ -21619,7 +21619,7 @@
       <c r="AD186" t="inlineStr"/>
       <c r="AE186" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF186" t="inlineStr">
@@ -21731,7 +21731,7 @@
       </c>
       <c r="AE187" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:57</t>
+          <t>2026-10-30 15:13:47</t>
         </is>
       </c>
       <c r="AF187" t="inlineStr">
@@ -21859,7 +21859,7 @@
       </c>
       <c r="AE188" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF188" t="inlineStr">
@@ -21971,7 +21971,7 @@
       </c>
       <c r="AE189" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF189" t="inlineStr">
@@ -22083,7 +22083,7 @@
       </c>
       <c r="AE190" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF190" t="inlineStr">
@@ -22193,7 +22193,7 @@
       </c>
       <c r="AE191" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF191" t="inlineStr">
@@ -22305,7 +22305,7 @@
       </c>
       <c r="AE192" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF192" t="inlineStr">
@@ -22417,7 +22417,7 @@
       </c>
       <c r="AE193" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF193" t="inlineStr">
@@ -22527,7 +22527,7 @@
       </c>
       <c r="AE194" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF194" t="inlineStr">
@@ -22637,7 +22637,7 @@
       </c>
       <c r="AE195" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF195" t="inlineStr">
@@ -22753,7 +22753,7 @@
       </c>
       <c r="AE196" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF196" t="inlineStr">
@@ -22865,7 +22865,7 @@
       </c>
       <c r="AE197" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF197" t="inlineStr">
@@ -22985,7 +22985,7 @@
       </c>
       <c r="AE198" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF198" t="inlineStr">
@@ -23097,7 +23097,7 @@
       </c>
       <c r="AE199" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF199" t="inlineStr">
@@ -23213,7 +23213,7 @@
       </c>
       <c r="AE200" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF200" t="inlineStr">
@@ -23323,7 +23323,7 @@
       </c>
       <c r="AE201" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF201" t="inlineStr">
@@ -23433,7 +23433,7 @@
       </c>
       <c r="AE202" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF202" t="inlineStr">
@@ -23553,7 +23553,7 @@
       </c>
       <c r="AE203" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF203" t="inlineStr">
@@ -23667,7 +23667,7 @@
       </c>
       <c r="AE204" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF204" t="inlineStr">
@@ -23781,7 +23781,7 @@
       </c>
       <c r="AE205" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF205" t="inlineStr">
@@ -23901,7 +23901,7 @@
       </c>
       <c r="AE206" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF206" t="inlineStr">
@@ -24011,7 +24011,7 @@
       </c>
       <c r="AE207" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF207" t="inlineStr">
@@ -24127,7 +24127,7 @@
       </c>
       <c r="AE208" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF208" t="inlineStr">
@@ -24239,7 +24239,7 @@
       </c>
       <c r="AE209" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:57</t>
+          <t>2026-10-30 15:13:47</t>
         </is>
       </c>
       <c r="AF209" t="inlineStr">
@@ -24351,7 +24351,7 @@
       </c>
       <c r="AE210" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF210" t="inlineStr">
@@ -24465,7 +24465,7 @@
       </c>
       <c r="AE211" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF211" t="inlineStr">
@@ -24579,7 +24579,7 @@
       </c>
       <c r="AE212" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF212" t="inlineStr">
@@ -24689,7 +24689,7 @@
       </c>
       <c r="AE213" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:55</t>
+          <t>2026-10-30 15:13:46</t>
         </is>
       </c>
       <c r="AF213" t="inlineStr">
@@ -24799,7 +24799,7 @@
       </c>
       <c r="AE214" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF214" t="inlineStr">
@@ -24909,7 +24909,7 @@
       </c>
       <c r="AE215" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF215" t="inlineStr">
@@ -25019,7 +25019,7 @@
       </c>
       <c r="AE216" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF216" t="inlineStr">
@@ -25133,7 +25133,7 @@
       </c>
       <c r="AE217" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF217" t="inlineStr">
@@ -25247,7 +25247,7 @@
       </c>
       <c r="AE218" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF218" t="inlineStr">
@@ -25375,7 +25375,7 @@
       </c>
       <c r="AE219" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF219" t="inlineStr">
@@ -25503,7 +25503,7 @@
       </c>
       <c r="AE220" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF220" t="inlineStr">
@@ -25613,7 +25613,7 @@
       </c>
       <c r="AE221" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF221" t="inlineStr">
@@ -25723,7 +25723,7 @@
       </c>
       <c r="AE222" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF222" t="inlineStr">
@@ -25843,7 +25843,7 @@
       </c>
       <c r="AE223" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF223" t="inlineStr">
@@ -25957,7 +25957,7 @@
       </c>
       <c r="AE224" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF224" t="inlineStr">
@@ -26067,7 +26067,7 @@
       </c>
       <c r="AE225" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF225" t="inlineStr">
@@ -26195,7 +26195,7 @@
       </c>
       <c r="AE226" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF226" t="inlineStr">
@@ -26317,7 +26317,7 @@
       <c r="AD227" t="inlineStr"/>
       <c r="AE227" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF227" t="inlineStr">
@@ -26445,7 +26445,7 @@
       </c>
       <c r="AE228" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF228" t="inlineStr">
@@ -26561,7 +26561,7 @@
       </c>
       <c r="AE229" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24:09</t>
+          <t>2026-10-30 15:14:02</t>
         </is>
       </c>
       <c r="AF229" t="inlineStr">
@@ -26689,7 +26689,7 @@
       </c>
       <c r="AE230" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF230" t="inlineStr">
@@ -26821,7 +26821,7 @@
       </c>
       <c r="AE231" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF231" t="inlineStr">
@@ -26935,7 +26935,7 @@
       </c>
       <c r="AE232" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF232" t="inlineStr">
@@ -27057,7 +27057,7 @@
       <c r="AD233" t="inlineStr"/>
       <c r="AE233" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF233" t="inlineStr">
@@ -27169,7 +27169,7 @@
       </c>
       <c r="AE234" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF234" t="inlineStr">
@@ -27269,7 +27269,7 @@
       </c>
       <c r="AE235" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF235" t="inlineStr">
@@ -27379,7 +27379,7 @@
       </c>
       <c r="AE236" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF236" t="inlineStr">
@@ -27495,7 +27495,7 @@
       </c>
       <c r="AE237" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF237" t="inlineStr">
@@ -27611,7 +27611,7 @@
       </c>
       <c r="AE238" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF238" t="inlineStr">
@@ -27739,7 +27739,7 @@
       </c>
       <c r="AE239" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF239" t="inlineStr">
@@ -27849,7 +27849,7 @@
       </c>
       <c r="AE240" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF240" t="inlineStr">
@@ -27963,7 +27963,7 @@
       </c>
       <c r="AE241" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF241" t="inlineStr">
@@ -28077,7 +28077,7 @@
       </c>
       <c r="AE242" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF242" t="inlineStr">
@@ -28191,7 +28191,7 @@
       </c>
       <c r="AE243" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF243" t="inlineStr">
@@ -28301,7 +28301,7 @@
       </c>
       <c r="AE244" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF244" t="inlineStr">
@@ -28415,7 +28415,7 @@
       </c>
       <c r="AE245" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF245" t="inlineStr">
@@ -28525,7 +28525,7 @@
       </c>
       <c r="AE246" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF246" t="inlineStr">
@@ -28637,7 +28637,7 @@
       </c>
       <c r="AE247" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF247" t="inlineStr">
@@ -28753,7 +28753,7 @@
       </c>
       <c r="AE248" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24:09</t>
+          <t>2026-10-30 15:14:02</t>
         </is>
       </c>
       <c r="AF248" t="inlineStr">
@@ -28869,7 +28869,7 @@
       </c>
       <c r="AE249" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF249" t="inlineStr">
@@ -28981,7 +28981,7 @@
       </c>
       <c r="AE250" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF250" t="inlineStr">
@@ -29093,7 +29093,7 @@
       </c>
       <c r="AE251" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF251" t="inlineStr">
@@ -29205,7 +29205,7 @@
       </c>
       <c r="AE252" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF252" t="inlineStr">
@@ -29333,7 +29333,7 @@
       </c>
       <c r="AE253" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:57</t>
+          <t>2026-10-30 15:13:47</t>
         </is>
       </c>
       <c r="AF253" t="inlineStr">
@@ -29443,7 +29443,7 @@
       </c>
       <c r="AE254" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF254" t="inlineStr">
@@ -29563,7 +29563,7 @@
       </c>
       <c r="AE255" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF255" t="inlineStr">
@@ -29685,7 +29685,7 @@
       <c r="AD256" t="inlineStr"/>
       <c r="AE256" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF256" t="inlineStr">
@@ -29811,7 +29811,7 @@
       <c r="AD257" t="inlineStr"/>
       <c r="AE257" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF257" t="inlineStr">
@@ -29937,7 +29937,7 @@
       <c r="AD258" t="inlineStr"/>
       <c r="AE258" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF258" t="inlineStr">
@@ -30053,7 +30053,7 @@
       </c>
       <c r="AE259" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24:09</t>
+          <t>2026-10-30 15:14:02</t>
         </is>
       </c>
       <c r="AF259" t="inlineStr">
@@ -30167,7 +30167,7 @@
       </c>
       <c r="AE260" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF260" t="inlineStr">
@@ -30281,7 +30281,7 @@
       </c>
       <c r="AE261" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF261" t="inlineStr">
@@ -30395,7 +30395,7 @@
       </c>
       <c r="AE262" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF262" t="inlineStr">
@@ -30515,7 +30515,7 @@
       </c>
       <c r="AE263" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF263" t="inlineStr">
@@ -30635,7 +30635,7 @@
       </c>
       <c r="AE264" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF264" t="inlineStr">
@@ -30745,7 +30745,7 @@
       </c>
       <c r="AE265" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF265" t="inlineStr">
@@ -30855,7 +30855,7 @@
       </c>
       <c r="AE266" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF266" t="inlineStr">
@@ -30965,7 +30965,7 @@
       </c>
       <c r="AE267" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF267" t="inlineStr">
@@ -31081,7 +31081,7 @@
       </c>
       <c r="AE268" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF268" t="inlineStr">
@@ -31209,7 +31209,7 @@
       </c>
       <c r="AE269" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF269" t="inlineStr">
@@ -31321,7 +31321,7 @@
       </c>
       <c r="AE270" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF270" t="inlineStr">
@@ -31433,7 +31433,7 @@
       </c>
       <c r="AE271" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF271" t="inlineStr">
@@ -31547,7 +31547,7 @@
       </c>
       <c r="AE272" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:55</t>
+          <t>2026-10-30 15:13:46</t>
         </is>
       </c>
       <c r="AF272" t="inlineStr">
@@ -31657,7 +31657,7 @@
       </c>
       <c r="AE273" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF273" t="inlineStr">
@@ -31767,7 +31767,7 @@
       </c>
       <c r="AE274" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF274" t="inlineStr">
@@ -31879,7 +31879,7 @@
       </c>
       <c r="AE275" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF275" t="inlineStr">
@@ -31989,7 +31989,7 @@
       </c>
       <c r="AE276" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF276" t="inlineStr">
@@ -32109,7 +32109,7 @@
       </c>
       <c r="AE277" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF277" t="inlineStr">
@@ -32225,7 +32225,7 @@
       </c>
       <c r="AE278" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF278" t="inlineStr">
@@ -32341,7 +32341,7 @@
       </c>
       <c r="AE279" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF279" t="inlineStr">
@@ -32469,7 +32469,7 @@
       </c>
       <c r="AE280" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF280" t="inlineStr">
@@ -32581,7 +32581,7 @@
       </c>
       <c r="AE281" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF281" t="inlineStr">
@@ -32693,7 +32693,7 @@
       </c>
       <c r="AE282" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF282" t="inlineStr">
@@ -32805,7 +32805,7 @@
       </c>
       <c r="AE283" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF283" t="inlineStr">
@@ -32921,7 +32921,7 @@
       </c>
       <c r="AE284" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF284" t="inlineStr">
@@ -33031,7 +33031,7 @@
       </c>
       <c r="AE285" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF285" t="inlineStr">
@@ -33151,7 +33151,7 @@
       </c>
       <c r="AE286" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF286" t="inlineStr">
@@ -33261,7 +33261,7 @@
       </c>
       <c r="AE287" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF287" t="inlineStr">
@@ -33381,7 +33381,7 @@
       </c>
       <c r="AE288" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF288" t="inlineStr">
@@ -33491,7 +33491,7 @@
       </c>
       <c r="AE289" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF289" t="inlineStr">
@@ -33601,7 +33601,7 @@
       </c>
       <c r="AE290" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:55</t>
+          <t>2026-10-30 15:13:46</t>
         </is>
       </c>
       <c r="AF290" t="inlineStr">
@@ -33711,7 +33711,7 @@
       </c>
       <c r="AE291" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF291" t="inlineStr">
@@ -33821,7 +33821,7 @@
       </c>
       <c r="AE292" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF292" t="inlineStr">
@@ -33935,7 +33935,7 @@
       </c>
       <c r="AE293" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF293" t="inlineStr">
@@ -34045,7 +34045,7 @@
       </c>
       <c r="AE294" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF294" t="inlineStr">
@@ -34157,7 +34157,7 @@
       </c>
       <c r="AE295" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF295" t="inlineStr">
@@ -34267,7 +34267,7 @@
       </c>
       <c r="AE296" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF296" t="inlineStr">
@@ -34387,7 +34387,7 @@
       </c>
       <c r="AE297" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF297" t="inlineStr">
@@ -34499,7 +34499,7 @@
       </c>
       <c r="AE298" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF298" t="inlineStr">
@@ -34609,7 +34609,7 @@
       </c>
       <c r="AE299" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF299" t="inlineStr">
@@ -34733,7 +34733,7 @@
       </c>
       <c r="AE300" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:57</t>
+          <t>2026-10-30 15:13:47</t>
         </is>
       </c>
       <c r="AF300" t="inlineStr">
@@ -34857,7 +34857,7 @@
       </c>
       <c r="AE301" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:57</t>
+          <t>2026-10-30 15:13:47</t>
         </is>
       </c>
       <c r="AF301" t="inlineStr">
@@ -34967,7 +34967,7 @@
       </c>
       <c r="AE302" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF302" t="inlineStr">
@@ -35077,7 +35077,7 @@
       </c>
       <c r="AE303" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF303" t="inlineStr">
@@ -35187,7 +35187,7 @@
       </c>
       <c r="AE304" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF304" t="inlineStr">
@@ -35299,7 +35299,7 @@
       </c>
       <c r="AE305" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF305" t="inlineStr">
@@ -35409,7 +35409,7 @@
       </c>
       <c r="AE306" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF306" t="inlineStr">
@@ -35519,7 +35519,7 @@
       </c>
       <c r="AE307" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF307" t="inlineStr">
@@ -35647,7 +35647,7 @@
       </c>
       <c r="AE308" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF308" t="inlineStr">
@@ -35753,7 +35753,7 @@
       </c>
       <c r="AE309" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF309" t="inlineStr">
@@ -35865,7 +35865,7 @@
       </c>
       <c r="AE310" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF310" t="inlineStr">
@@ -35981,7 +35981,7 @@
       </c>
       <c r="AE311" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24:09</t>
+          <t>2026-10-30 15:14:02</t>
         </is>
       </c>
       <c r="AF311" t="inlineStr">
@@ -36097,7 +36097,7 @@
       </c>
       <c r="AE312" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24:09</t>
+          <t>2026-10-30 15:14:02</t>
         </is>
       </c>
       <c r="AF312" t="inlineStr">
@@ -36207,7 +36207,7 @@
       </c>
       <c r="AE313" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF313" t="inlineStr">
@@ -36317,7 +36317,7 @@
       </c>
       <c r="AE314" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF314" t="inlineStr">
@@ -36433,7 +36433,7 @@
       </c>
       <c r="AE315" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24:09</t>
+          <t>2026-10-30 15:14:02</t>
         </is>
       </c>
       <c r="AF315" t="inlineStr">
@@ -36549,7 +36549,7 @@
       </c>
       <c r="AE316" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24:09</t>
+          <t>2026-10-30 15:14:02</t>
         </is>
       </c>
       <c r="AF316" t="inlineStr">
@@ -36659,7 +36659,7 @@
       </c>
       <c r="AE317" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF317" t="inlineStr">
@@ -36775,7 +36775,7 @@
       </c>
       <c r="AE318" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24:09</t>
+          <t>2026-10-30 15:14:02</t>
         </is>
       </c>
       <c r="AF318" t="inlineStr">
@@ -36885,7 +36885,7 @@
       </c>
       <c r="AE319" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF319" t="inlineStr">
@@ -36995,7 +36995,7 @@
       </c>
       <c r="AE320" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF320" t="inlineStr">
@@ -37105,7 +37105,7 @@
       </c>
       <c r="AE321" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF321" t="inlineStr">
@@ -37205,7 +37205,7 @@
       </c>
       <c r="AE322" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF322" t="inlineStr">
@@ -37315,7 +37315,7 @@
       </c>
       <c r="AE323" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF323" t="inlineStr">
@@ -37427,7 +37427,7 @@
       </c>
       <c r="AE324" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF324" t="inlineStr">
@@ -37537,7 +37537,7 @@
       </c>
       <c r="AE325" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF325" t="inlineStr">
@@ -37657,7 +37657,7 @@
       </c>
       <c r="AE326" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF326" t="inlineStr">
@@ -37769,7 +37769,7 @@
       </c>
       <c r="AE327" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF327" t="inlineStr">
@@ -37879,7 +37879,7 @@
       </c>
       <c r="AE328" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF328" t="inlineStr">
@@ -37991,7 +37991,7 @@
       </c>
       <c r="AE329" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF329" t="inlineStr">
@@ -38107,7 +38107,7 @@
       </c>
       <c r="AE330" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF330" t="inlineStr">
@@ -38219,7 +38219,7 @@
       </c>
       <c r="AE331" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF331" t="inlineStr">
@@ -38329,7 +38329,7 @@
       </c>
       <c r="AE332" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF332" t="inlineStr">
@@ -38445,7 +38445,7 @@
       </c>
       <c r="AE333" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF333" t="inlineStr">
@@ -38555,7 +38555,7 @@
       </c>
       <c r="AE334" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF334" t="inlineStr">
@@ -38681,7 +38681,7 @@
       <c r="AD335" t="inlineStr"/>
       <c r="AE335" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF335" t="inlineStr">
@@ -38809,7 +38809,7 @@
       </c>
       <c r="AE336" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF336" t="inlineStr">
@@ -38921,7 +38921,7 @@
       </c>
       <c r="AE337" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF337" t="inlineStr">
@@ -39021,7 +39021,7 @@
       </c>
       <c r="AE338" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF338" t="inlineStr">
@@ -39121,7 +39121,7 @@
       </c>
       <c r="AE339" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF339" t="inlineStr">
@@ -39235,7 +39235,7 @@
       </c>
       <c r="AE340" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF340" t="inlineStr">
@@ -39349,7 +39349,7 @@
       </c>
       <c r="AE341" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF341" t="inlineStr">
@@ -39449,7 +39449,7 @@
       </c>
       <c r="AE342" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF342" t="inlineStr">
@@ -39569,7 +39569,7 @@
       </c>
       <c r="AE343" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF343" t="inlineStr">
@@ -39681,7 +39681,7 @@
       </c>
       <c r="AE344" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF344" t="inlineStr">
@@ -39793,7 +39793,7 @@
       </c>
       <c r="AE345" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF345" t="inlineStr">
@@ -39907,7 +39907,7 @@
       </c>
       <c r="AE346" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF346" t="inlineStr">
@@ -40017,7 +40017,7 @@
       </c>
       <c r="AE347" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:55</t>
+          <t>2026-10-30 15:13:46</t>
         </is>
       </c>
       <c r="AF347" t="inlineStr">
@@ -40127,7 +40127,7 @@
       </c>
       <c r="AE348" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:55</t>
+          <t>2026-10-30 15:13:46</t>
         </is>
       </c>
       <c r="AF348" t="inlineStr">
@@ -40259,7 +40259,7 @@
       </c>
       <c r="AE349" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF349" t="inlineStr">
@@ -40387,7 +40387,7 @@
       </c>
       <c r="AE350" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF350" t="inlineStr">
@@ -40515,7 +40515,7 @@
       </c>
       <c r="AE351" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF351" t="inlineStr">
@@ -40643,7 +40643,7 @@
       </c>
       <c r="AE352" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF352" t="inlineStr">
@@ -40755,7 +40755,7 @@
       </c>
       <c r="AE353" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF353" t="inlineStr">
@@ -40867,7 +40867,7 @@
       </c>
       <c r="AE354" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF354" t="inlineStr">
@@ -40977,7 +40977,7 @@
       </c>
       <c r="AE355" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF355" t="inlineStr">
@@ -41087,7 +41087,7 @@
       </c>
       <c r="AE356" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF356" t="inlineStr">
@@ -41215,7 +41215,7 @@
       </c>
       <c r="AE357" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF357" t="inlineStr">
@@ -41325,7 +41325,7 @@
       </c>
       <c r="AE358" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF358" t="inlineStr">
@@ -41453,7 +41453,7 @@
       </c>
       <c r="AE359" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF359" t="inlineStr">
@@ -41565,7 +41565,7 @@
       </c>
       <c r="AE360" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF360" t="inlineStr">
@@ -41677,7 +41677,7 @@
       </c>
       <c r="AE361" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF361" t="inlineStr">
@@ -41787,7 +41787,7 @@
       </c>
       <c r="AE362" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF362" t="inlineStr">
@@ -41907,7 +41907,7 @@
       </c>
       <c r="AE363" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF363" t="inlineStr">
@@ -42031,7 +42031,7 @@
       </c>
       <c r="AE364" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF364" t="inlineStr">
@@ -42155,7 +42155,7 @@
       </c>
       <c r="AE365" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF365" t="inlineStr">
@@ -42279,7 +42279,7 @@
       </c>
       <c r="AE366" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF366" t="inlineStr">
@@ -42391,7 +42391,7 @@
       </c>
       <c r="AE367" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF367" t="inlineStr">
@@ -42507,7 +42507,7 @@
       </c>
       <c r="AE368" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF368" t="inlineStr">
@@ -42619,7 +42619,7 @@
       </c>
       <c r="AE369" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:57</t>
+          <t>2026-10-30 15:13:47</t>
         </is>
       </c>
       <c r="AF369" t="inlineStr">
@@ -42747,7 +42747,7 @@
       </c>
       <c r="AE370" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:57</t>
+          <t>2026-10-30 15:13:47</t>
         </is>
       </c>
       <c r="AF370" t="inlineStr">
@@ -42875,7 +42875,7 @@
       </c>
       <c r="AE371" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF371" t="inlineStr">
@@ -42987,7 +42987,7 @@
       </c>
       <c r="AE372" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF372" t="inlineStr">
@@ -43099,7 +43099,7 @@
       </c>
       <c r="AE373" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF373" t="inlineStr">
@@ -43209,7 +43209,7 @@
       </c>
       <c r="AE374" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF374" t="inlineStr">
@@ -43319,7 +43319,7 @@
       </c>
       <c r="AE375" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF375" t="inlineStr">
@@ -43435,7 +43435,7 @@
       </c>
       <c r="AE376" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF376" t="inlineStr">
@@ -43547,7 +43547,7 @@
       </c>
       <c r="AE377" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF377" t="inlineStr">
@@ -43667,7 +43667,7 @@
       </c>
       <c r="AE378" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF378" t="inlineStr">
@@ -43795,7 +43795,7 @@
       </c>
       <c r="AE379" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF379" t="inlineStr">
@@ -43911,7 +43911,7 @@
       </c>
       <c r="AE380" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF380" t="inlineStr">
@@ -44011,7 +44011,7 @@
       </c>
       <c r="AE381" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF381" t="inlineStr">
@@ -44123,7 +44123,7 @@
       </c>
       <c r="AE382" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF382" t="inlineStr">
@@ -44251,7 +44251,7 @@
       </c>
       <c r="AE383" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF383" t="inlineStr">
@@ -44375,7 +44375,7 @@
       </c>
       <c r="AE384" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:57</t>
+          <t>2026-10-30 15:13:47</t>
         </is>
       </c>
       <c r="AF384" t="inlineStr">
@@ -44485,7 +44485,7 @@
       </c>
       <c r="AE385" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF385" t="inlineStr">
@@ -44595,7 +44595,7 @@
       </c>
       <c r="AE386" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF386" t="inlineStr">
@@ -44705,7 +44705,7 @@
       </c>
       <c r="AE387" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF387" t="inlineStr">
@@ -44815,7 +44815,7 @@
       </c>
       <c r="AE388" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF388" t="inlineStr">
@@ -44935,7 +44935,7 @@
       </c>
       <c r="AE389" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF389" t="inlineStr">
@@ -45045,7 +45045,7 @@
       </c>
       <c r="AE390" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF390" t="inlineStr">
@@ -45155,7 +45155,7 @@
       </c>
       <c r="AE391" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF391" t="inlineStr">
@@ -45265,7 +45265,7 @@
       </c>
       <c r="AE392" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF392" t="inlineStr">
@@ -45385,7 +45385,7 @@
       </c>
       <c r="AE393" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF393" t="inlineStr">
@@ -45505,7 +45505,7 @@
       </c>
       <c r="AE394" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF394" t="inlineStr">
@@ -45625,7 +45625,7 @@
       </c>
       <c r="AE395" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF395" t="inlineStr">
@@ -45745,7 +45745,7 @@
       </c>
       <c r="AE396" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF396" t="inlineStr">
@@ -45861,7 +45861,7 @@
       </c>
       <c r="AE397" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24:09</t>
+          <t>2026-10-30 15:14:02</t>
         </is>
       </c>
       <c r="AF397" t="inlineStr">
@@ -45977,7 +45977,7 @@
       </c>
       <c r="AE398" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24:09</t>
+          <t>2026-10-30 15:14:02</t>
         </is>
       </c>
       <c r="AF398" t="inlineStr">
@@ -46093,7 +46093,7 @@
       </c>
       <c r="AE399" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24:09</t>
+          <t>2026-10-30 15:14:02</t>
         </is>
       </c>
       <c r="AF399" t="inlineStr">
@@ -46205,7 +46205,7 @@
       </c>
       <c r="AE400" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF400" t="inlineStr">
@@ -46317,7 +46317,7 @@
       </c>
       <c r="AE401" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF401" t="inlineStr">
@@ -46437,7 +46437,7 @@
       </c>
       <c r="AE402" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF402" t="inlineStr">
@@ -46549,7 +46549,7 @@
       </c>
       <c r="AE403" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF403" t="inlineStr">
@@ -46665,7 +46665,7 @@
       </c>
       <c r="AE404" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24:09</t>
+          <t>2026-10-30 15:14:02</t>
         </is>
       </c>
       <c r="AF404" t="inlineStr">
@@ -46775,7 +46775,7 @@
       </c>
       <c r="AE405" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:55</t>
+          <t>2026-10-30 15:13:46</t>
         </is>
       </c>
       <c r="AF405" t="inlineStr">
@@ -46885,7 +46885,7 @@
       </c>
       <c r="AE406" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF406" t="inlineStr">
@@ -47001,7 +47001,7 @@
       </c>
       <c r="AE407" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF407" t="inlineStr">
@@ -47113,7 +47113,7 @@
       </c>
       <c r="AE408" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF408" t="inlineStr">
@@ -47223,7 +47223,7 @@
       </c>
       <c r="AE409" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF409" t="inlineStr">
@@ -47335,7 +47335,7 @@
       </c>
       <c r="AE410" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF410" t="inlineStr">
@@ -47447,7 +47447,7 @@
       </c>
       <c r="AE411" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF411" t="inlineStr">
@@ -47559,7 +47559,7 @@
       </c>
       <c r="AE412" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF412" t="inlineStr">
@@ -47679,7 +47679,7 @@
       </c>
       <c r="AE413" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF413" t="inlineStr">
@@ -47807,7 +47807,7 @@
       </c>
       <c r="AE414" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF414" t="inlineStr">
@@ -47927,7 +47927,7 @@
       </c>
       <c r="AE415" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF415" t="inlineStr">
@@ -48055,7 +48055,7 @@
       </c>
       <c r="AE416" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF416" t="inlineStr">
@@ -48167,7 +48167,7 @@
       </c>
       <c r="AE417" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF417" t="inlineStr">
@@ -48277,7 +48277,7 @@
       </c>
       <c r="AE418" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF418" t="inlineStr">
@@ -48387,7 +48387,7 @@
       </c>
       <c r="AE419" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF419" t="inlineStr">
@@ -48499,7 +48499,7 @@
       </c>
       <c r="AE420" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF420" t="inlineStr">
@@ -48611,7 +48611,7 @@
       </c>
       <c r="AE421" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF421" t="inlineStr">
@@ -48721,7 +48721,7 @@
       </c>
       <c r="AE422" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF422" t="inlineStr">
@@ -48837,7 +48837,7 @@
       </c>
       <c r="AE423" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF423" t="inlineStr">
@@ -48947,7 +48947,7 @@
       </c>
       <c r="AE424" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF424" t="inlineStr">
@@ -49059,7 +49059,7 @@
       </c>
       <c r="AE425" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF425" t="inlineStr">
@@ -49169,7 +49169,7 @@
       </c>
       <c r="AE426" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF426" t="inlineStr">
@@ -49279,7 +49279,7 @@
       </c>
       <c r="AE427" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF427" t="inlineStr">
@@ -49407,7 +49407,7 @@
       </c>
       <c r="AE428" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF428" t="inlineStr">
@@ -49519,7 +49519,7 @@
       </c>
       <c r="AE429" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF429" t="inlineStr">
@@ -49647,7 +49647,7 @@
       </c>
       <c r="AE430" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF430" t="inlineStr">
@@ -49759,7 +49759,7 @@
       </c>
       <c r="AE431" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF431" t="inlineStr">
@@ -49869,7 +49869,7 @@
       </c>
       <c r="AE432" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF432" t="inlineStr">
@@ -49979,7 +49979,7 @@
       </c>
       <c r="AE433" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF433" t="inlineStr">
@@ -50089,7 +50089,7 @@
       </c>
       <c r="AE434" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF434" t="inlineStr">
@@ -50201,7 +50201,7 @@
       </c>
       <c r="AE435" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF435" t="inlineStr">
@@ -50311,7 +50311,7 @@
       </c>
       <c r="AE436" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF436" t="inlineStr">
@@ -50439,7 +50439,7 @@
       </c>
       <c r="AE437" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF437" t="inlineStr">
@@ -50551,7 +50551,7 @@
       </c>
       <c r="AE438" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF438" t="inlineStr">
@@ -50661,7 +50661,7 @@
       </c>
       <c r="AE439" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF439" t="inlineStr">
@@ -50771,7 +50771,7 @@
       </c>
       <c r="AE440" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF440" t="inlineStr">
@@ -50881,7 +50881,7 @@
       </c>
       <c r="AE441" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF441" t="inlineStr">
@@ -50991,7 +50991,7 @@
       </c>
       <c r="AE442" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF442" t="inlineStr">
@@ -51101,7 +51101,7 @@
       </c>
       <c r="AE443" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF443" t="inlineStr">
@@ -51213,7 +51213,7 @@
       </c>
       <c r="AE444" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF444" t="inlineStr">
@@ -51341,7 +51341,7 @@
       </c>
       <c r="AE445" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF445" t="inlineStr">
@@ -51451,7 +51451,7 @@
       </c>
       <c r="AE446" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF446" t="inlineStr">
@@ -51561,7 +51561,7 @@
       </c>
       <c r="AE447" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF447" t="inlineStr">
@@ -51673,7 +51673,7 @@
       </c>
       <c r="AE448" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:57</t>
+          <t>2026-10-30 15:13:47</t>
         </is>
       </c>
       <c r="AF448" t="inlineStr">
@@ -51783,7 +51783,7 @@
       </c>
       <c r="AE449" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF449" t="inlineStr">
@@ -51895,7 +51895,7 @@
       </c>
       <c r="AE450" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF450" t="inlineStr">
@@ -52023,7 +52023,7 @@
       </c>
       <c r="AE451" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF451" t="inlineStr">
@@ -52133,7 +52133,7 @@
       </c>
       <c r="AE452" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF452" t="inlineStr">
@@ -52245,7 +52245,7 @@
       </c>
       <c r="AE453" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF453" t="inlineStr">
@@ -52355,7 +52355,7 @@
       </c>
       <c r="AE454" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF454" t="inlineStr">
@@ -52465,7 +52465,7 @@
       </c>
       <c r="AE455" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF455" t="inlineStr">
@@ -52575,7 +52575,7 @@
       </c>
       <c r="AE456" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF456" t="inlineStr">
@@ -52675,7 +52675,7 @@
       </c>
       <c r="AE457" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF457" t="inlineStr">
@@ -52785,7 +52785,7 @@
       </c>
       <c r="AE458" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF458" t="inlineStr">
@@ -52885,7 +52885,7 @@
       </c>
       <c r="AE459" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF459" t="inlineStr">
@@ -52995,7 +52995,7 @@
       </c>
       <c r="AE460" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF460" t="inlineStr">
@@ -53123,7 +53123,7 @@
       </c>
       <c r="AE461" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF461" t="inlineStr">
@@ -53233,7 +53233,7 @@
       </c>
       <c r="AE462" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF462" t="inlineStr">
@@ -53343,7 +53343,7 @@
       </c>
       <c r="AE463" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF463" t="inlineStr">
@@ -53453,7 +53453,7 @@
       </c>
       <c r="AE464" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF464" t="inlineStr">
@@ -53563,7 +53563,7 @@
       </c>
       <c r="AE465" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF465" t="inlineStr">
@@ -53673,7 +53673,7 @@
       </c>
       <c r="AE466" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF466" t="inlineStr">
@@ -53783,7 +53783,7 @@
       </c>
       <c r="AE467" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF467" t="inlineStr">
@@ -53893,7 +53893,7 @@
       </c>
       <c r="AE468" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF468" t="inlineStr">
@@ -54003,7 +54003,7 @@
       </c>
       <c r="AE469" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF469" t="inlineStr">
@@ -54131,7 +54131,7 @@
       </c>
       <c r="AE470" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF470" t="inlineStr">
@@ -54243,7 +54243,7 @@
       </c>
       <c r="AE471" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF471" t="inlineStr">
@@ -54343,7 +54343,7 @@
       </c>
       <c r="AE472" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF472" t="inlineStr">
@@ -54453,7 +54453,7 @@
       </c>
       <c r="AE473" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF473" t="inlineStr">
@@ -54567,7 +54567,7 @@
       </c>
       <c r="AE474" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF474" t="inlineStr">
@@ -54677,7 +54677,7 @@
       </c>
       <c r="AE475" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF475" t="inlineStr">
@@ -54777,7 +54777,7 @@
       </c>
       <c r="AE476" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF476" t="inlineStr">
@@ -54889,7 +54889,7 @@
       </c>
       <c r="AE477" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF477" t="inlineStr">
@@ -55001,7 +55001,7 @@
       </c>
       <c r="AE478" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF478" t="inlineStr">
@@ -55111,7 +55111,7 @@
       </c>
       <c r="AE479" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF479" t="inlineStr">
@@ -55223,7 +55223,7 @@
       </c>
       <c r="AE480" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF480" t="inlineStr">
@@ -55335,7 +55335,7 @@
       </c>
       <c r="AE481" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF481" t="inlineStr">
@@ -55445,7 +55445,7 @@
       </c>
       <c r="AE482" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF482" t="inlineStr">
@@ -55573,7 +55573,7 @@
       </c>
       <c r="AE483" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF483" t="inlineStr">
@@ -55705,7 +55705,7 @@
       </c>
       <c r="AE484" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF484" t="inlineStr">
@@ -55837,7 +55837,7 @@
       </c>
       <c r="AE485" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF485" t="inlineStr">
@@ -55969,7 +55969,7 @@
       </c>
       <c r="AE486" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF486" t="inlineStr">
@@ -56093,7 +56093,7 @@
       </c>
       <c r="AE487" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:57</t>
+          <t>2026-10-30 15:13:47</t>
         </is>
       </c>
       <c r="AF487" t="inlineStr">
@@ -56205,7 +56205,7 @@
       </c>
       <c r="AE488" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF488" t="inlineStr">
@@ -56305,7 +56305,7 @@
       </c>
       <c r="AE489" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF489" t="inlineStr">
@@ -56425,7 +56425,7 @@
       </c>
       <c r="AE490" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF490" t="inlineStr">
@@ -56541,7 +56541,7 @@
       </c>
       <c r="AE491" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF491" t="inlineStr">
@@ -56653,7 +56653,7 @@
       </c>
       <c r="AE492" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF492" t="inlineStr">
@@ -56775,7 +56775,7 @@
       <c r="AD493" t="inlineStr"/>
       <c r="AE493" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF493" t="inlineStr">
@@ -56887,7 +56887,7 @@
       </c>
       <c r="AE494" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF494" t="inlineStr">
@@ -56997,7 +56997,7 @@
       </c>
       <c r="AE495" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF495" t="inlineStr">
@@ -57107,7 +57107,7 @@
       </c>
       <c r="AE496" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF496" t="inlineStr">
@@ -57217,7 +57217,7 @@
       </c>
       <c r="AE497" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF497" t="inlineStr">
@@ -57327,7 +57327,7 @@
       </c>
       <c r="AE498" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF498" t="inlineStr">
@@ -57455,7 +57455,7 @@
       </c>
       <c r="AE499" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF499" t="inlineStr">
@@ -57571,7 +57571,7 @@
       </c>
       <c r="AE500" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF500" t="inlineStr">
@@ -57681,7 +57681,7 @@
       </c>
       <c r="AE501" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF501" t="inlineStr">
@@ -57809,7 +57809,7 @@
       </c>
       <c r="AE502" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF502" t="inlineStr">
@@ -57937,7 +57937,7 @@
       </c>
       <c r="AE503" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF503" t="inlineStr">
@@ -58065,7 +58065,7 @@
       </c>
       <c r="AE504" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF504" t="inlineStr">
@@ -58193,7 +58193,7 @@
       </c>
       <c r="AE505" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF505" t="inlineStr">
@@ -58305,7 +58305,7 @@
       </c>
       <c r="AE506" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF506" t="inlineStr">
@@ -58415,7 +58415,7 @@
       </c>
       <c r="AE507" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF507" t="inlineStr">
@@ -58543,7 +58543,7 @@
       </c>
       <c r="AE508" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF508" t="inlineStr">
@@ -58655,7 +58655,7 @@
       </c>
       <c r="AE509" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF509" t="inlineStr">
@@ -58767,7 +58767,7 @@
       </c>
       <c r="AE510" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF510" t="inlineStr">
@@ -58883,7 +58883,7 @@
       </c>
       <c r="AE511" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF511" t="inlineStr">
@@ -58995,7 +58995,7 @@
       </c>
       <c r="AE512" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF512" t="inlineStr">
@@ -59107,7 +59107,7 @@
       </c>
       <c r="AE513" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF513" t="inlineStr">
@@ -59219,7 +59219,7 @@
       </c>
       <c r="AE514" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF514" t="inlineStr">
@@ -59331,7 +59331,7 @@
       </c>
       <c r="AE515" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF515" t="inlineStr">
@@ -59451,7 +59451,7 @@
       </c>
       <c r="AE516" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF516" t="inlineStr">
@@ -59561,7 +59561,7 @@
       </c>
       <c r="AE517" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF517" t="inlineStr">
@@ -59689,7 +59689,7 @@
       </c>
       <c r="AE518" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF518" t="inlineStr">
@@ -59809,7 +59809,7 @@
       </c>
       <c r="AE519" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF519" t="inlineStr">
@@ -59921,7 +59921,7 @@
       </c>
       <c r="AE520" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF520" t="inlineStr">
@@ -60033,7 +60033,7 @@
       </c>
       <c r="AE521" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF521" t="inlineStr">
@@ -60133,7 +60133,7 @@
       </c>
       <c r="AE522" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF522" t="inlineStr">
@@ -60249,7 +60249,7 @@
       </c>
       <c r="AE523" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF523" t="inlineStr">
@@ -60359,7 +60359,7 @@
       </c>
       <c r="AE524" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF524" t="inlineStr">
@@ -60471,7 +60471,7 @@
       </c>
       <c r="AE525" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF525" t="inlineStr">
@@ -60581,7 +60581,7 @@
       </c>
       <c r="AE526" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF526" t="inlineStr">
@@ -60693,7 +60693,7 @@
       </c>
       <c r="AE527" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF527" t="inlineStr">
@@ -60805,7 +60805,7 @@
       </c>
       <c r="AE528" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF528" t="inlineStr">
@@ -60905,7 +60905,7 @@
       </c>
       <c r="AE529" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF529" t="inlineStr">
@@ -61015,7 +61015,7 @@
       </c>
       <c r="AE530" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF530" t="inlineStr">
@@ -61127,7 +61127,7 @@
       </c>
       <c r="AE531" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF531" t="inlineStr">
@@ -61237,7 +61237,7 @@
       </c>
       <c r="AE532" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF532" t="inlineStr">
@@ -61347,7 +61347,7 @@
       </c>
       <c r="AE533" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF533" t="inlineStr">
@@ -61459,7 +61459,7 @@
       </c>
       <c r="AE534" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF534" t="inlineStr">
@@ -61569,7 +61569,7 @@
       </c>
       <c r="AE535" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF535" t="inlineStr">
@@ -61679,7 +61679,7 @@
       </c>
       <c r="AE536" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF536" t="inlineStr">
@@ -61789,7 +61789,7 @@
       </c>
       <c r="AE537" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF537" t="inlineStr">
@@ -61909,7 +61909,7 @@
       </c>
       <c r="AE538" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF538" t="inlineStr">
@@ -62033,7 +62033,7 @@
       </c>
       <c r="AE539" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:57</t>
+          <t>2026-10-30 15:13:47</t>
         </is>
       </c>
       <c r="AF539" t="inlineStr">
@@ -62143,7 +62143,7 @@
       </c>
       <c r="AE540" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF540" t="inlineStr">
@@ -62255,7 +62255,7 @@
       </c>
       <c r="AE541" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF541" t="inlineStr">
@@ -62365,7 +62365,7 @@
       </c>
       <c r="AE542" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF542" t="inlineStr">
@@ -62477,7 +62477,7 @@
       </c>
       <c r="AE543" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF543" t="inlineStr">
@@ -62589,7 +62589,7 @@
       </c>
       <c r="AE544" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF544" t="inlineStr">
@@ -62699,7 +62699,7 @@
       </c>
       <c r="AE545" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF545" t="inlineStr">
@@ -62809,7 +62809,7 @@
       </c>
       <c r="AE546" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF546" t="inlineStr">
@@ -62919,7 +62919,7 @@
       </c>
       <c r="AE547" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF547" t="inlineStr">
@@ -63029,7 +63029,7 @@
       </c>
       <c r="AE548" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF548" t="inlineStr">
@@ -63139,7 +63139,7 @@
       </c>
       <c r="AE549" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF549" t="inlineStr">
@@ -63249,7 +63249,7 @@
       </c>
       <c r="AE550" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF550" t="inlineStr">
@@ -63361,7 +63361,7 @@
       </c>
       <c r="AE551" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF551" t="inlineStr">
@@ -63473,7 +63473,7 @@
       </c>
       <c r="AE552" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF552" t="inlineStr">
@@ -63585,7 +63585,7 @@
       </c>
       <c r="AE553" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF553" t="inlineStr">
@@ -63695,7 +63695,7 @@
       </c>
       <c r="AE554" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF554" t="inlineStr">
@@ -63807,7 +63807,7 @@
       </c>
       <c r="AE555" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF555" t="inlineStr">
@@ -63907,7 +63907,7 @@
       </c>
       <c r="AE556" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF556" t="inlineStr">
@@ -64017,7 +64017,7 @@
       </c>
       <c r="AE557" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF557" t="inlineStr">
@@ -64117,7 +64117,7 @@
       </c>
       <c r="AE558" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF558" t="inlineStr">
@@ -64217,7 +64217,7 @@
       </c>
       <c r="AE559" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF559" t="inlineStr">
@@ -64329,7 +64329,7 @@
       </c>
       <c r="AE560" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF560" t="inlineStr">
@@ -64441,7 +64441,7 @@
       </c>
       <c r="AE561" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF561" t="inlineStr">
@@ -64553,7 +64553,7 @@
       </c>
       <c r="AE562" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF562" t="inlineStr">
@@ -64663,7 +64663,7 @@
       </c>
       <c r="AE563" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF563" t="inlineStr">
@@ -64773,7 +64773,7 @@
       </c>
       <c r="AE564" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF564" t="inlineStr">
@@ -64883,7 +64883,7 @@
       </c>
       <c r="AE565" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF565" t="inlineStr">
@@ -64995,7 +64995,7 @@
       </c>
       <c r="AE566" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF566" t="inlineStr">
@@ -65105,7 +65105,7 @@
       </c>
       <c r="AE567" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF567" t="inlineStr">
@@ -65215,7 +65215,7 @@
       </c>
       <c r="AE568" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF568" t="inlineStr">
@@ -65325,7 +65325,7 @@
       </c>
       <c r="AE569" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF569" t="inlineStr">
@@ -65435,7 +65435,7 @@
       </c>
       <c r="AE570" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF570" t="inlineStr">
@@ -65547,7 +65547,7 @@
       </c>
       <c r="AE571" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF571" t="inlineStr">
@@ -65659,7 +65659,7 @@
       </c>
       <c r="AE572" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF572" t="inlineStr">
@@ -65775,7 +65775,7 @@
       </c>
       <c r="AE573" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF573" t="inlineStr">
@@ -65903,7 +65903,7 @@
       </c>
       <c r="AE574" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF574" t="inlineStr">
@@ -66015,7 +66015,7 @@
       </c>
       <c r="AE575" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF575" t="inlineStr">
@@ -66125,7 +66125,7 @@
       </c>
       <c r="AE576" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF576" t="inlineStr">
@@ -66245,7 +66245,7 @@
       </c>
       <c r="AE577" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF577" t="inlineStr">
@@ -66355,7 +66355,7 @@
       </c>
       <c r="AE578" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF578" t="inlineStr">
@@ -66465,7 +66465,7 @@
       </c>
       <c r="AE579" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF579" t="inlineStr">
@@ -66575,7 +66575,7 @@
       </c>
       <c r="AE580" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF580" t="inlineStr">
@@ -66695,7 +66695,7 @@
       </c>
       <c r="AE581" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF581" t="inlineStr">
@@ -66811,7 +66811,7 @@
       </c>
       <c r="AE582" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF582" t="inlineStr">
@@ -66923,7 +66923,7 @@
       </c>
       <c r="AE583" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF583" t="inlineStr">
@@ -67043,7 +67043,7 @@
       </c>
       <c r="AE584" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF584" t="inlineStr">
@@ -67155,7 +67155,7 @@
       </c>
       <c r="AE585" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF585" t="inlineStr">
@@ -67255,7 +67255,7 @@
       </c>
       <c r="AE586" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF586" t="inlineStr">
@@ -67375,7 +67375,7 @@
       </c>
       <c r="AE587" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF587" t="inlineStr">
@@ -67485,7 +67485,7 @@
       </c>
       <c r="AE588" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF588" t="inlineStr">
@@ -67597,7 +67597,7 @@
       </c>
       <c r="AE589" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF589" t="inlineStr">
@@ -67713,7 +67713,7 @@
       </c>
       <c r="AE590" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF590" t="inlineStr">
@@ -67825,7 +67825,7 @@
       </c>
       <c r="AE591" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF591" t="inlineStr">
@@ -67937,7 +67937,7 @@
       </c>
       <c r="AE592" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF592" t="inlineStr">
@@ -68065,7 +68065,7 @@
       </c>
       <c r="AE593" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF593" t="inlineStr">
@@ -68175,7 +68175,7 @@
       </c>
       <c r="AE594" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF594" t="inlineStr">
@@ -68285,7 +68285,7 @@
       </c>
       <c r="AE595" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF595" t="inlineStr">
@@ -68395,7 +68395,7 @@
       </c>
       <c r="AE596" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF596" t="inlineStr">
@@ -68507,7 +68507,7 @@
       </c>
       <c r="AE597" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF597" t="inlineStr">
@@ -68635,7 +68635,7 @@
       </c>
       <c r="AE598" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF598" t="inlineStr">
@@ -68747,7 +68747,7 @@
       </c>
       <c r="AE599" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF599" t="inlineStr">
@@ -68859,7 +68859,7 @@
       </c>
       <c r="AE600" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF600" t="inlineStr">
@@ -68971,7 +68971,7 @@
       </c>
       <c r="AE601" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF601" t="inlineStr">
@@ -69071,7 +69071,7 @@
       </c>
       <c r="AE602" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF602" t="inlineStr">
@@ -69181,7 +69181,7 @@
       </c>
       <c r="AE603" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF603" t="inlineStr">
@@ -69291,7 +69291,7 @@
       </c>
       <c r="AE604" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF604" t="inlineStr">
@@ -69391,7 +69391,7 @@
       </c>
       <c r="AE605" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF605" t="inlineStr">
@@ -69501,7 +69501,7 @@
       </c>
       <c r="AE606" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF606" t="inlineStr">
@@ -69629,7 +69629,7 @@
       </c>
       <c r="AE607" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF607" t="inlineStr">
@@ -69739,7 +69739,7 @@
       </c>
       <c r="AE608" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF608" t="inlineStr">
@@ -69851,7 +69851,7 @@
       </c>
       <c r="AE609" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF609" t="inlineStr">
@@ -69961,7 +69961,7 @@
       </c>
       <c r="AE610" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF610" t="inlineStr">
@@ -70073,7 +70073,7 @@
       </c>
       <c r="AE611" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF611" t="inlineStr">
@@ -70183,7 +70183,7 @@
       </c>
       <c r="AE612" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF612" t="inlineStr">
@@ -70293,7 +70293,7 @@
       </c>
       <c r="AE613" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF613" t="inlineStr">
@@ -70393,7 +70393,7 @@
       </c>
       <c r="AE614" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF614" t="inlineStr">
@@ -70503,7 +70503,7 @@
       </c>
       <c r="AE615" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF615" t="inlineStr">
@@ -70615,7 +70615,7 @@
       </c>
       <c r="AE616" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF616" t="inlineStr">
@@ -70725,7 +70725,7 @@
       </c>
       <c r="AE617" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF617" t="inlineStr">
@@ -70835,7 +70835,7 @@
       </c>
       <c r="AE618" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF618" t="inlineStr">
@@ -70945,7 +70945,7 @@
       </c>
       <c r="AE619" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF619" t="inlineStr">
@@ -71055,7 +71055,7 @@
       </c>
       <c r="AE620" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF620" t="inlineStr">
@@ -71165,7 +71165,7 @@
       </c>
       <c r="AE621" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF621" t="inlineStr">
@@ -71275,7 +71275,7 @@
       </c>
       <c r="AE622" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF622" t="inlineStr">
@@ -71375,7 +71375,7 @@
       </c>
       <c r="AE623" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF623" t="inlineStr">
@@ -71485,7 +71485,7 @@
       </c>
       <c r="AE624" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF624" t="inlineStr">
@@ -71595,7 +71595,7 @@
       </c>
       <c r="AE625" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF625" t="inlineStr">
@@ -71707,7 +71707,7 @@
       </c>
       <c r="AE626" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF626" t="inlineStr">
@@ -71817,7 +71817,7 @@
       </c>
       <c r="AE627" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF627" t="inlineStr">
@@ -71929,7 +71929,7 @@
       </c>
       <c r="AE628" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF628" t="inlineStr">
@@ -72039,7 +72039,7 @@
       </c>
       <c r="AE629" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF629" t="inlineStr">
@@ -72149,7 +72149,7 @@
       </c>
       <c r="AE630" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF630" t="inlineStr">
@@ -72259,7 +72259,7 @@
       </c>
       <c r="AE631" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF631" t="inlineStr">
@@ -72369,7 +72369,7 @@
       </c>
       <c r="AE632" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF632" t="inlineStr">
@@ -72479,7 +72479,7 @@
       </c>
       <c r="AE633" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF633" t="inlineStr">
@@ -72591,7 +72591,7 @@
       </c>
       <c r="AE634" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF634" t="inlineStr">
@@ -72701,7 +72701,7 @@
       </c>
       <c r="AE635" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF635" t="inlineStr">
@@ -72813,7 +72813,7 @@
       </c>
       <c r="AE636" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF636" t="inlineStr">
@@ -72925,7 +72925,7 @@
       </c>
       <c r="AE637" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF637" t="inlineStr">
@@ -73035,7 +73035,7 @@
       </c>
       <c r="AE638" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF638" t="inlineStr">
@@ -73147,7 +73147,7 @@
       </c>
       <c r="AE639" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF639" t="inlineStr">
@@ -73259,7 +73259,7 @@
       </c>
       <c r="AE640" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF640" t="inlineStr">
@@ -73369,7 +73369,7 @@
       </c>
       <c r="AE641" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF641" t="inlineStr">
@@ -73479,7 +73479,7 @@
       </c>
       <c r="AE642" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF642" t="inlineStr">
@@ -73589,7 +73589,7 @@
       </c>
       <c r="AE643" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF643" t="inlineStr">
@@ -73699,7 +73699,7 @@
       </c>
       <c r="AE644" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF644" t="inlineStr">
@@ -73799,7 +73799,7 @@
       </c>
       <c r="AE645" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF645" t="inlineStr">
@@ -73911,7 +73911,7 @@
       </c>
       <c r="AE646" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF646" t="inlineStr">
@@ -74021,7 +74021,7 @@
       </c>
       <c r="AE647" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF647" t="inlineStr">
@@ -74131,7 +74131,7 @@
       </c>
       <c r="AE648" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF648" t="inlineStr">
@@ -74259,7 +74259,7 @@
       </c>
       <c r="AE649" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF649" t="inlineStr">
@@ -74371,7 +74371,7 @@
       </c>
       <c r="AE650" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF650" t="inlineStr">
@@ -74483,7 +74483,7 @@
       </c>
       <c r="AE651" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF651" t="inlineStr">
@@ -74611,7 +74611,7 @@
       </c>
       <c r="AE652" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF652" t="inlineStr">
@@ -74723,7 +74723,7 @@
       </c>
       <c r="AE653" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF653" t="inlineStr">
@@ -74851,7 +74851,7 @@
       </c>
       <c r="AE654" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF654" t="inlineStr">
@@ -74979,7 +74979,7 @@
       </c>
       <c r="AE655" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="AF655" t="inlineStr">
@@ -75091,7 +75091,7 @@
       </c>
       <c r="AE656" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF656" t="inlineStr">
@@ -75203,7 +75203,7 @@
       </c>
       <c r="AE657" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF657" t="inlineStr">
@@ -75313,7 +75313,7 @@
       </c>
       <c r="AE658" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF658" t="inlineStr">
@@ -75425,7 +75425,7 @@
       </c>
       <c r="AE659" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF659" t="inlineStr">
@@ -75535,7 +75535,7 @@
       </c>
       <c r="AE660" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF660" t="inlineStr">
@@ -75645,7 +75645,7 @@
       </c>
       <c r="AE661" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF661" t="inlineStr">
@@ -75757,7 +75757,7 @@
       </c>
       <c r="AE662" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF662" t="inlineStr">
@@ -75869,7 +75869,7 @@
       </c>
       <c r="AE663" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF663" t="inlineStr">
@@ -75981,7 +75981,7 @@
       </c>
       <c r="AE664" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF664" t="inlineStr">
@@ -76091,7 +76091,7 @@
       </c>
       <c r="AE665" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF665" t="inlineStr">
@@ -76201,7 +76201,7 @@
       </c>
       <c r="AE666" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF666" t="inlineStr">
@@ -76313,7 +76313,7 @@
       </c>
       <c r="AE667" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF667" t="inlineStr">
@@ -76425,7 +76425,7 @@
       </c>
       <c r="AE668" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF668" t="inlineStr">
@@ -76535,7 +76535,7 @@
       </c>
       <c r="AE669" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF669" t="inlineStr">
@@ -76647,7 +76647,7 @@
       </c>
       <c r="AE670" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF670" t="inlineStr">
@@ -76757,7 +76757,7 @@
       </c>
       <c r="AE671" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF671" t="inlineStr">
@@ -76857,7 +76857,7 @@
       </c>
       <c r="AE672" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF672" t="inlineStr">
@@ -76967,7 +76967,7 @@
       </c>
       <c r="AE673" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF673" t="inlineStr">
@@ -77079,7 +77079,7 @@
       </c>
       <c r="AE674" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF674" t="inlineStr">
@@ -77189,7 +77189,7 @@
       </c>
       <c r="AE675" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF675" t="inlineStr">
@@ -77301,7 +77301,7 @@
       </c>
       <c r="AE676" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF676" t="inlineStr">
@@ -77411,7 +77411,7 @@
       </c>
       <c r="AE677" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF677" t="inlineStr">
@@ -77521,7 +77521,7 @@
       </c>
       <c r="AE678" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF678" t="inlineStr">
@@ -77631,7 +77631,7 @@
       </c>
       <c r="AE679" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF679" t="inlineStr">
@@ -77741,7 +77741,7 @@
       </c>
       <c r="AE680" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF680" t="inlineStr">
@@ -77851,7 +77851,7 @@
       </c>
       <c r="AE681" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF681" t="inlineStr">
@@ -77963,7 +77963,7 @@
       </c>
       <c r="AE682" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF682" t="inlineStr">
@@ -78073,7 +78073,7 @@
       </c>
       <c r="AE683" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF683" t="inlineStr">
@@ -78183,7 +78183,7 @@
       </c>
       <c r="AE684" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF684" t="inlineStr">
@@ -78293,7 +78293,7 @@
       </c>
       <c r="AE685" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF685" t="inlineStr">
@@ -78405,7 +78405,7 @@
       </c>
       <c r="AE686" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF686" t="inlineStr">
@@ -78515,7 +78515,7 @@
       </c>
       <c r="AE687" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF687" t="inlineStr">
@@ -78627,7 +78627,7 @@
       </c>
       <c r="AE688" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF688" t="inlineStr">
@@ -78739,7 +78739,7 @@
       </c>
       <c r="AE689" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF689" t="inlineStr">
@@ -78839,7 +78839,7 @@
       </c>
       <c r="AE690" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF690" t="inlineStr">
@@ -78949,7 +78949,7 @@
       </c>
       <c r="AE691" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF691" t="inlineStr">
@@ -79061,7 +79061,7 @@
       </c>
       <c r="AE692" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF692" t="inlineStr">
@@ -79173,7 +79173,7 @@
       </c>
       <c r="AE693" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF693" t="inlineStr">
@@ -79285,7 +79285,7 @@
       </c>
       <c r="AE694" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF694" t="inlineStr">
@@ -79397,7 +79397,7 @@
       </c>
       <c r="AE695" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF695" t="inlineStr">
@@ -79507,7 +79507,7 @@
       </c>
       <c r="AE696" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF696" t="inlineStr">
@@ -79617,7 +79617,7 @@
       </c>
       <c r="AE697" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF697" t="inlineStr">
@@ -79729,7 +79729,7 @@
       </c>
       <c r="AE698" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF698" t="inlineStr">
@@ -79839,7 +79839,7 @@
       </c>
       <c r="AE699" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF699" t="inlineStr">
@@ -79951,7 +79951,7 @@
       </c>
       <c r="AE700" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF700" t="inlineStr">
@@ -80051,7 +80051,7 @@
       </c>
       <c r="AE701" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF701" t="inlineStr">
@@ -80161,7 +80161,7 @@
       </c>
       <c r="AE702" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF702" t="inlineStr">
@@ -80273,7 +80273,7 @@
       </c>
       <c r="AE703" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF703" t="inlineStr">
@@ -80383,7 +80383,7 @@
       <c r="AD704" t="inlineStr"/>
       <c r="AE704" t="inlineStr">
         <is>
-          <t>2026-10-30 10:24:09</t>
+          <t>2026-10-30 15:14:02</t>
         </is>
       </c>
       <c r="AF704" t="inlineStr">
@@ -80495,7 +80495,7 @@
       </c>
       <c r="AE705" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF705" t="inlineStr">
@@ -80607,7 +80607,7 @@
       </c>
       <c r="AE706" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF706" t="inlineStr">
@@ -80717,7 +80717,7 @@
       </c>
       <c r="AE707" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF707" t="inlineStr">
@@ -80829,7 +80829,7 @@
       </c>
       <c r="AE708" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF708" t="inlineStr">
@@ -80929,7 +80929,7 @@
       </c>
       <c r="AE709" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF709" t="inlineStr">
@@ -81029,7 +81029,7 @@
       </c>
       <c r="AE710" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF710" t="inlineStr">
@@ -81129,7 +81129,7 @@
       </c>
       <c r="AE711" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF711" t="inlineStr">
@@ -81241,7 +81241,7 @@
       </c>
       <c r="AE712" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF712" t="inlineStr">
@@ -81341,7 +81341,7 @@
       </c>
       <c r="AE713" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF713" t="inlineStr">
@@ -81451,7 +81451,7 @@
       </c>
       <c r="AE714" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF714" t="inlineStr">
@@ -81551,7 +81551,7 @@
       </c>
       <c r="AE715" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF715" t="inlineStr">
@@ -81663,7 +81663,7 @@
       </c>
       <c r="AE716" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF716" t="inlineStr">
@@ -81775,7 +81775,7 @@
       </c>
       <c r="AE717" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF717" t="inlineStr">
@@ -81887,7 +81887,7 @@
       </c>
       <c r="AE718" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF718" t="inlineStr">
@@ -81999,7 +81999,7 @@
       </c>
       <c r="AE719" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF719" t="inlineStr">
@@ -82099,7 +82099,7 @@
       </c>
       <c r="AE720" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF720" t="inlineStr">
@@ -82211,7 +82211,7 @@
       </c>
       <c r="AE721" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF721" t="inlineStr">
@@ -82321,7 +82321,7 @@
       </c>
       <c r="AE722" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF722" t="inlineStr">
@@ -82433,7 +82433,7 @@
       </c>
       <c r="AE723" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF723" t="inlineStr">
@@ -82533,7 +82533,7 @@
       </c>
       <c r="AE724" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF724" t="inlineStr">
@@ -82633,7 +82633,7 @@
       </c>
       <c r="AE725" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF725" t="inlineStr">
@@ -82733,7 +82733,7 @@
       </c>
       <c r="AE726" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF726" t="inlineStr">
@@ -82833,7 +82833,7 @@
       </c>
       <c r="AE727" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF727" t="inlineStr">
@@ -82945,7 +82945,7 @@
       </c>
       <c r="AE728" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF728" t="inlineStr">
@@ -83057,7 +83057,7 @@
       </c>
       <c r="AE729" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF729" t="inlineStr">
@@ -83157,7 +83157,7 @@
       </c>
       <c r="AE730" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF730" t="inlineStr">
@@ -83267,7 +83267,7 @@
       </c>
       <c r="AE731" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF731" t="inlineStr">
@@ -83379,7 +83379,7 @@
       </c>
       <c r="AE732" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF732" t="inlineStr">
@@ -83491,7 +83491,7 @@
       </c>
       <c r="AE733" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF733" t="inlineStr">
@@ -83603,7 +83603,7 @@
       </c>
       <c r="AE734" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF734" t="inlineStr">
@@ -83715,7 +83715,7 @@
       </c>
       <c r="AE735" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF735" t="inlineStr">
@@ -83827,7 +83827,7 @@
       </c>
       <c r="AE736" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF736" t="inlineStr">
@@ -83939,7 +83939,7 @@
       </c>
       <c r="AE737" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF737" t="inlineStr">
@@ -84051,7 +84051,7 @@
       </c>
       <c r="AE738" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF738" t="inlineStr">
@@ -84151,7 +84151,7 @@
       </c>
       <c r="AE739" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF739" t="inlineStr">
@@ -84251,7 +84251,7 @@
       </c>
       <c r="AE740" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF740" t="inlineStr">
@@ -84363,7 +84363,7 @@
       </c>
       <c r="AE741" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:44</t>
+          <t>2026-10-30 15:13:33</t>
         </is>
       </c>
       <c r="AF741" t="inlineStr">
@@ -84463,7 +84463,7 @@
       </c>
       <c r="AE742" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF742" t="inlineStr">
@@ -84563,7 +84563,7 @@
       </c>
       <c r="AE743" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF743" t="inlineStr">
@@ -84663,7 +84663,7 @@
       </c>
       <c r="AE744" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF744" t="inlineStr">
@@ -84773,7 +84773,7 @@
       </c>
       <c r="AE745" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF745" t="inlineStr">
@@ -84873,7 +84873,7 @@
       </c>
       <c r="AE746" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF746" t="inlineStr">
@@ -84983,7 +84983,7 @@
       </c>
       <c r="AE747" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF747" t="inlineStr">
@@ -85065,7 +85065,7 @@
       <c r="AD748" t="inlineStr"/>
       <c r="AE748" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF748" t="inlineStr">
@@ -85147,7 +85147,7 @@
       <c r="AD749" t="inlineStr"/>
       <c r="AE749" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF749" t="inlineStr">
@@ -85229,7 +85229,7 @@
       <c r="AD750" t="inlineStr"/>
       <c r="AE750" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF750" t="inlineStr">
@@ -85311,7 +85311,7 @@
       <c r="AD751" t="inlineStr"/>
       <c r="AE751" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:51</t>
+          <t>2026-10-30 15:13:41</t>
         </is>
       </c>
       <c r="AF751" t="inlineStr">
